--- a/Washington_Jun22-25_Utilization_Estimate.xlsx
+++ b/Washington_Jun22-25_Utilization_Estimate.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Utilization Estimate" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consolidation Report" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Util — Flagging Filter" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Included GSF rows" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -61,7 +61,7 @@
       <sz val="32"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -75,12 +75,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -90,7 +90,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00C65911"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4B183"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -120,31 +130,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -510,335 +520,346 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GSF Utilization estimate — Washington · 22–25 Jun 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+          <t>Washington Jun 22–25 — Utilization with Manual Flagging / Guardian SmartFlagging filter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: Onyx daily paste · Physical sets S=6 (Washington, previously confirmed) · Formula: In Field Sets ÷ (S × weekdays)</t>
+          <t>User-stated utilization for this period: 24%. Revised numerator: count GSF Sent only on Job Type = Manual Flagging OR Guardian SmartFlagging (exclude Off-Road Work, Road Closure, etc. even if GSF Sent &gt; 0).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>DAILY TOTALS</t>
+          <t>COMPARISON</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Staff Requested</t>
+          <t>In Field Sets</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Staff Sent</t>
+          <t>On Hand (6×4)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Saved</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>GSF Sent</t>
+          <t>Utilization</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>22-Jun-26</t>
+          <t>A. All job types (prior estimate)</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>B. Manual Flagging + Guardian SmartFlagging only</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>User-stated</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr"/>
+      <c r="C8" s="7" t="inlineStr"/>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>REVISED FORMULA</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Eligible GSF Sent</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>12 devices</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Sum GSF Sent where Job Type ∈ {Manual Flagging, Guardian SmartFlagging}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>In Field Sets</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>12 ÷ 2 = 6</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>2 devices = 1 set</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Sets on Hand</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>6 × 4 = 24</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Washington sets × Mon–Thu weekdays</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Utilization %</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>6 ÷ 24 = 25.0%</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Matches stated 24% within 1 pt (25% exact)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>GSF ROWS EXCLUDED (not Manual Flagging / Guardian SmartFlagging)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>GSF Sent</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Why excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>23-Jun-26</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>South Central Power Company</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Off-Road Work</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>23-Jun-26</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>24-Jun-26</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="D8" s="5" t="n">
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>Job type not Manual Flagging or Guardian SmartFlagging</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>25-Jun-26</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>South Central Power Company</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>Off-Road Work</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="6" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>Job type not Manual Flagging or Guardian SmartFlagging</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>25-Jun-26</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>PERIOD</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n">
-        <v>130</v>
-      </c>
-      <c r="C10" s="7" t="n">
-        <v>121</v>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>UTILIZATION</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>GSF Sent (devices)</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>2+6+4+6 from daily Totals</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>In Field Sets</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>18 ÷ 2 = 9</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>Also = count of rows with GSF Sent&gt;0 = 9</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>Physical sets S</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>Washington inventory</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>Weekdays W</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>4 (Mon 22 – Thu 25)</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>No weekend in this range</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>Sets on Hand</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>6 × 4 = 24</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>S × W</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>Utilization %</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>9 ÷ 24 = 37.50%</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>In Field Sets ÷ Sets on Hand</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>Mix % (approx)</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>9 ÷ 59 = 15.3%</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>GSF ticket-days ÷ all ticket-days</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>PREDICTED UTILIZATION</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="48" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>38%</t>
-        </is>
-      </c>
-      <c r="C23" s="13" t="inlineStr">
-        <is>
-          <t>Washington · 6 sets · In Field=9 · On Hand=24 · 22–25 Jun 2026</t>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>Thayer Power &amp; Communication Line Construction Co., LLC</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Road Closure</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>Job type not Manual Flagging or Guardian SmartFlagging</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>These 6 devices (3 sets) were in the all-types numerator (37.5%) but dropped for the flagging-only model (25%).</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Note: paste had "12%-24%" on the 25-Jun Totals line — that does not match the validated formula (9÷24=37.5%).</t>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>PREDICTED (flagging filter)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>vs stated 24% · In Field=6 · On Hand=24 · excluded 3 non-flagging GSF set-days</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A12:C12"/>
+  <mergeCells count="7">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A17:E17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -850,36 +871,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Onyx Consolidation — Washington · 22-Jun-26 through 25-Jun-26</t>
+          <t>GSF rows counted in flagging-only numerator</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Sub-Contractor</t>
-        </is>
-      </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Job Type</t>
@@ -887,248 +899,169 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Staff Requested</t>
+          <t>GSF Sent</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Staff Sent</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Saved</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>GSF Sent</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>9 AEP</t>
-        </is>
-      </c>
-      <c r="B4" s="14" t="inlineStr">
-        <is>
-          <t>9 AEP</t>
-        </is>
-      </c>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>6 Manual Flagging; 2 Guardian SmartFlagging; 1 Arrow Board</t>
-        </is>
-      </c>
-      <c r="D4" s="14" t="n">
-        <v>19</v>
-      </c>
-      <c r="E4" s="14" t="n">
-        <v>17</v>
-      </c>
-      <c r="F4" s="14" t="n">
+          <t>Sets (=GSF/2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>22-Jun-26</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Henkels &amp; McCoy</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Guardian SmartFlagging</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="G4" s="14" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>11 Henkels &amp; McCoy</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr"/>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>4 Manual Flagging; 3 Guardian SmartFlagging; 3 Road Closure; 1 Off-Road Work</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="n">
-        <v>22</v>
-      </c>
-      <c r="E5" s="14" t="n">
-        <v>19</v>
-      </c>
-      <c r="F5" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" s="14" t="n">
+      <c r="E4" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>23-Jun-26</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>AEP</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Guardian SmartFlagging</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>23-Jun-26</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Henkels &amp; McCoy</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Guardian SmartFlagging</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>24-Jun-26</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Henkels &amp; McCoy</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Guardian SmartFlagging</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>24-Jun-26</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>South Central Power Company</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Guardian SmartFlagging</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>25-Jun-26</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>AEP</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Guardian SmartFlagging</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="E10" s="17" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>4 South Central Power Company</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>4 Thayer Power &amp; Communication Line Construction Co., LLC</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>2 Off-Road Work; 1 Guardian SmartFlagging; 1 Manual Flagging</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="E6" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" s="14" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>4 Thayer Power &amp; Communication Line Construction Co., LLC</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr"/>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>2 Manual Flagging; 2 Road Closure</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="n">
-        <v>9</v>
-      </c>
-      <c r="E7" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="F7" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="14" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>4 Verizon</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>4 Lambert's Cable - PA</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>4 Manual Flagging</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="n">
-        <v>14</v>
-      </c>
-      <c r="E8" s="15" t="n">
-        <v>14</v>
-      </c>
-      <c r="F8" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>24 Verizon</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>24 Verizon</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>21 Manual Flagging; 1 Arrow Board; 1 Lane Closure; 1 Road Closure</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="n">
-        <v>54</v>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>54</v>
-      </c>
-      <c r="F9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>3 W.D. Wright Contracting, Inc.</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr"/>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>2 Internal Labour; 1 Staging</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Totals</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n">
-        <v>130</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>121</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>22-Jun-26 through 25-Jun-26</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>